--- a/SylviaNG.Community/Community_Engagement_Features_v2.xlsx
+++ b/SylviaNG.Community/Community_Engagement_Features_v2.xlsx
@@ -1,85 +1,245 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abusu\Desktop\INTERN_PROJECT\Community_engagement_system\CES_Phase1_F1\SylviaNG.Community-master\SylviaNG.Community-master\SylviaNG.Community\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F85DAE-B73A-41CD-ABF0-1296A82F4C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement Features" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Community Engagement Features" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Feature Item</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Employee Profiles &amp; Directory</t>
+  </si>
+  <si>
+    <t>A centralized employee directory where employees maintain professional profiles containing their photo, designation, department, branch, contact information, skills, interests, achievements, and community contributions, and can mark individual contact fields (phone, email, extension) as public or private. Employees can search and discover colleagues across the organization, making it easier to collaborate, identify subject matter experts, and build connections beyond their immediate team. HR and Admin can create and deactivate employee profiles.</t>
+  </si>
+  <si>
+    <t>Notification Center</t>
+  </si>
+  <si>
+    <t>Sends in-app alerts to employees for recognitions received, survey invites and reminders, marketplace buyer/seller messages and interest in their listings, @mentions and reactions or comments on their posts, newly assigned tasks and approaching task due dates, and being added to a team as supervisor or member — so nothing important gets missed. Employees can turn each notification category on or off individually. HR and Admin receive the same notifications as any other employee for items addressed to them; pending moderation reports and marketplace listing approvals are reviewed through the Moderation Queue and Dashboard rather than as push notifications.</t>
+  </si>
+  <si>
+    <t>Social Hub &amp; Feed Management</t>
+  </si>
+  <si>
+    <t>Recognition</t>
+  </si>
+  <si>
+    <t>Lets employees recognize each other for things like teamwork, leadership, innovation, customer focus, excellence, and integrity, searching for the right colleague by name, Department, or Branch. Managers can also give recognition, and HR and Admin can award company-wide titles like Employee of the Month or Innovation Champion. Recognitions appear on a dedicated public wall, separate from the general Social Hub feed, where others can view and react to them.</t>
+  </si>
+  <si>
+    <t>Surveys &amp; Feedback</t>
+  </si>
+  <si>
+    <t>Marketplace</t>
+  </si>
+  <si>
+    <t>An internal marketplace where employees can negotiate, sell, request to buy, rent, exchange, or give away items in categories like electronics, furniture, books, vehicles, phones, appliances, and fashion. Each listing includes a title, description, category, price, photos, condition, and location, and can be searched or filtered the same way. Interested buyers can message the seller and track the conversation. Listings move through stages like draft, pending, active, or rejected; employee-submitted listings need HR or Admin approval before going live, while listings created by Admin go live immediately. Employees can also report listings that look fraudulent, inappropriate, or spammy.</t>
+  </si>
+  <si>
+    <t>Target-Based To-Do (Team &amp; Individual Tasks)</t>
+  </si>
+  <si>
+    <t>Lets a supervisor create teams (naming members and, for HR/Admin, any supervisor) and assign to-do tasks or targets directly to one or more subordinates, with a clear description, due date, and priority, and cancel a task after it's assigned. Each task can be tracked through stages like assigned, in progress, and completed, with the subordinate able to update status and add progress notes, and reminders are sent as the due date approaches. Supervisors get a view of all tasks they've assigned, who's on track, and what's overdue, so follow-ups are easy without leaving the platform. A dedicated My Teams screen lists every team company-wide; a supervisor can edit or delete only the teams they personally supervise, while employees see only the team(s) they belong to in a read-only view. Supervisors, HR, and Admin can also assign a task directly to any employee company-wide, outside of a team, searchable by Department and Branch - these appear to the recipient as a separate Individual Tasks list with the same status tracking and reminders. Any employee can be assigned as supervisor of one team while being a subordinate or member of another, and can belong to more than one team at a time.</t>
+  </si>
+  <si>
+    <t>Dashboard Widgets</t>
+  </si>
+  <si>
+    <t>Quick-glance dashboards for three audiences. Employees see their pending surveys, recognition received, my tasks, and recent activity. Supervisors additionally see a team task overview - who's on track and what's overdue - for everyone assigned to them. HR and Admin see the same company-wide stats view - active surveys, average survey participation, total recognitions given, and pending marketplace listings awaiting approval; HR currently sees this admin-style view only, not a blended employee view (flagged in Known Gaps below).</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Voting &amp; Election Management</t>
+  </si>
+  <si>
+    <t>A module enabling HR to organize secure and configurable elections where employees vote for nominated candidates — individual employees or teams, depending on the voting type. Elections can target the whole organization, a specific branch, department, team, or a hand-picked list of employees. HR configures single-choice or multiple-choice voting with minimum and maximum selectable candidates, and sets each election as anonymous (aggregated results only) or identified (HR can see each voter's identity and selections). HR can participate in voting when included in the eligible voter group.</t>
+  </si>
+  <si>
+    <t>Roles: Employee (any staff member) | Supervisor (an employee who supervises one or more teams, not a separate account type) | HR (an employee whose dashboard blends their own employee view with company-wide admin metrics) | Admin (a system administrator account, not an employee, with full company-wide access).</t>
+  </si>
+  <si>
+    <t>Status: Of Phase 1's 9 features, items 1–8 are fully implemented as a working prototype; item 9 (Voting &amp; Election Management) has been added to the Phase 1 scope and is not yet built. Phase 2 (Analytics, Global Search, Messenger) and Phase 4 (Events, Gamification) are not yet built; Phase 3 (AI Features) remains undecided.</t>
+  </si>
+  <si>
+    <t>Known Gaps &amp; Decisions Needed (from a code audit, before user stories are written): HR's dashboard is currently identical to Admin's rather than blending an employee view with company-wide stats - confirm intended behavior. Survey audience targeting for Department or Branch scope does not yet let you pick which department or branch, so it currently resolves to zero recipients - needs a fix before those scopes are usable. Team management and per-team task assignment pages have no route-level permission enforcement yet - access relies only on links being hidden in the UI, not real access control. Several modeled but unbuilt capabilities have no UI yet: survey matrix questions, marketplace listing edit/photos/My Listings, and editing or un-sending a recognition.</t>
+  </si>
+  <si>
+    <t>Phase: 02 Analytic Features</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Analytics &amp; Reporting Dashboard</t>
+  </si>
+  <si>
+    <t>Provides comprehensive reporting and analytics across the platform to help management understand employee engagement, participation, and activity trends. Dashboards can display metrics such as active users, posts created, reactions, comments, survey participation rates, recognition activity, task completion rates, and marketplace usage. Reports can be filtered by date range, branch, department, division, designation, or grade, allowing HR and leadership to identify trends, measure engagement initiatives, and make data-driven decisions.</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Global Search</t>
+  </si>
+  <si>
+    <t>A centralized search capability that allows employees to quickly find information across the entire platform. Users can search for employees, posts, comments, surveys, recognitions, marketplace listings, tasks, events, and other content using keywords or filters. Search results can be refined by category, department, date range, content type, or relevance, helping users locate information efficiently without navigating through multiple modules.</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Messenger</t>
+  </si>
+  <si>
+    <t>A real-time private messaging tool that lets employees chat one-on-one or in groups directly within the platform. Users can send text messages, images, files, and voice notes, and see delivery/read receipts and typing indicators. Group chats support adding/removing members, naming the group, and assigning an admin. Employees can search past conversations, pin important chats, mute notifications for specific threads, and react to individual messages (like, love, etc.). Users can also share posts, marketplace listings, or event invites directly into a chat. HR and Admin can access moderation tools to review reported conversations for policy violations, without infringing on regular employee privacy. Notifications for new messages integrate with the platform's existing Notification Center.</t>
+  </si>
+  <si>
+    <t>Phase:3 AI Features</t>
+  </si>
+  <si>
+    <t>Not decided yet</t>
+  </si>
+  <si>
+    <t>Phase:4 Gamification Features</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Events &amp; Activities Management</t>
+  </si>
+  <si>
+    <t>A platform for organizing and managing company events such as workshops, training programs, town halls, volunteer initiatives, sports activities, celebrations, and social gatherings. Events can include schedules, locations, participation limits, organizers, attachments, and announcements. Employees can browse upcoming events, view details, and stay informed about organizational activities.</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Event Registration &amp; Attendance</t>
+  </si>
+  <si>
+    <t>Allows employees to register for events and indicate attendance status through options such as Going, Maybe, or Not Going. Organizers can monitor registrations, manage attendee lists, track participation, and send reminders before the event. Attendance records can be maintained for future reporting and engagement analysis.</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Gamification &amp; Employee Engagement</t>
+  </si>
+  <si>
+    <t>A participation-based engagement system that encourages employees to actively contribute to the platform. Employees earn points for activities such as creating posts, receiving reactions, participating in surveys, attending events, completing assigned tasks, and recognizing colleagues. The system promotes healthy competition and motivates ongoing participation throughout the organization.</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Achievement Badges &amp; Recognition Levels</t>
+  </si>
+  <si>
+    <t>Allows employees to unlock achievement badges and progress through engagement levels based on milestones and participation. Examples include First Contributor, Team Player, Community Champion, Survey Advocate, and Recognition Star. Badges and levels are displayed on employee profiles and recognition feeds to celebrate accomplishments and encourage continued involvement.</t>
+  </si>
+  <si>
+    <t>A tool to build and send surveys using formats like short answer, long answer, multiple choice, checkboxes, dropdowns, rating scales, NPS, and matrix questions. Covers different survey types - engagement, satisfaction, pulse, event feedback, training feedback, or custom - and can be anonymous or named, mandatory or optional. Surveys can target the whole company, a department, or a branch, and are sent out immediately on publish. Results show participation rate along with average rating and NPS per question. It also enables employees to create and manage interest-based groups to foster collaboration, communication, and community engagement within the organization. Employees can create public or private groups, where public groups are open for any employee to join, while private groups require approval from the group creator or group administrators before membership is granted. Group members can create posts, share updates, and interact within their groups. Posts from public groups are also displayed on the organization's global social feed, whereas posts from private groups remain visible only to group members. Group creators can manage members, roles, and group settings, while HR has administrative access to all groups with the ability to moderate, edit, or remove groups, members, and content when necessary.</t>
+  </si>
+  <si>
+    <t>A company-wide social feed where employees can post text updates, photos, videos, polls, and announcements, and can edit or delete their own posts and comments. Each post's visibility can be set to everyone, a department, or a branch. People can react (Like, Love, Celebrate, Support, Insightful), comment, and tag colleagues. Polls are single-choice (a multi-choice option exists in the data model but has no UI control yet). HR and Admin can moderate content by hiding or removing posts, locking comments, and reviewing reported items. The module enables employees to create and manage interest-based groups to foster collaboration, communication, and community engagement within the organization. Employees can create public or private groups, where public groups are open for any employee to join, while private groups require approval from the group creator or group administrators before membership is granted. Group members can create posts, share updates, and interact within their groups. Posts from public groups are also displayed on the organization's global social feed, whereas posts from private groups remain visible only to group members. Group creators can manage members, roles, and group settings, while HR has administrative access to all groups with the ability to moderate, edit, or remove groups, members, and content when necessary.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F4E79"/>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <charset val="1"/>
-      <sz val="10"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <charset val="1"/>
-      <b val="1"/>
-      <color rgb="FF1F4E79"/>
-      <sz val="10"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <sz val="10"/>
-    </font>
-    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="14"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -242,65 +402,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -310,16 +470,16 @@
   <dxfs count="8">
     <dxf>
       <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
         <name val="Arial"/>
         <charset val="1"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <condense val="0"/>
-        <color auto="1"/>
-        <extend val="0"/>
-        <sz val="10"/>
-        <vertAlign val="baseline"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
@@ -344,17 +504,17 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1F4E79"/>
         <name val="Arial"/>
         <charset val="1"/>
-        <b val="1"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <condense val="0"/>
-        <color rgb="FF1F4E79"/>
-        <extend val="0"/>
-        <sz val="10"/>
-        <vertAlign val="baseline"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
@@ -381,16 +541,16 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
         <name val="Arial"/>
         <charset val="1"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <condense val="0"/>
-        <color auto="1"/>
-        <extend val="0"/>
-        <sz val="10"/>
-        <vertAlign val="baseline"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
@@ -454,18 +614,18 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="2"/>
-        <b val="1"/>
+        <b/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <condense val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <extend val="0"/>
-        <sz val="11"/>
-        <vertAlign val="baseline"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
@@ -556,16 +716,24 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:C10" headerRowCount="1" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4" totalsRowBorderDxfId="3">
-  <autoFilter ref="A1:C10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:C10" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4" totalsRowBorderDxfId="3">
+  <autoFilter ref="A1:C10" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="#" dataDxfId="2"/>
-    <tableColumn id="2" name="Feature Item" dataDxfId="1"/>
-    <tableColumn id="3" name="Description" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="#" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Feature Item" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -749,365 +917,255 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D34"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="5" customWidth="1" style="6" min="1" max="1"/>
-    <col width="32" customWidth="1" style="6" min="2" max="2"/>
-    <col width="102.21875" customWidth="1" style="6" min="3" max="3"/>
-    <col width="17.109375" customWidth="1" style="5" min="4" max="4"/>
-    <col width="8.6640625" customWidth="1" style="5" min="5" max="16384"/>
+    <col min="1" max="1" width="5" style="6" customWidth="1"/>
+    <col min="2" max="2" width="32" style="6" customWidth="1"/>
+    <col min="3" max="3" width="102.21875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Feature Item</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="66" customHeight="1">
-      <c r="A2" s="7" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>Employee Profiles &amp; Directory</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>A centralized employee directory where employees maintain professional profiles containing their photo, designation, department, branch, contact information, skills, interests, achievements, and community contributions, and can mark individual contact fields (phone, email, extension) as public or private. Employees can search and discover colleagues across the organization, making it easier to collaborate, identify subject matter experts, and build connections beyond their immediate team. HR and Admin can create and deactivate employee profiles.</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="79.2" customHeight="1">
-      <c r="A3" s="9" t="n">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Notification Center</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Sends in-app alerts to employees for recognitions received, survey invites and reminders, marketplace buyer/seller messages and interest in their listings, @mentions and reactions or comments on their posts, newly assigned tasks and approaching task due dates, and being added to a team as supervisor or member — so nothing important gets missed. Employees can turn each notification category on or off individually. HR and Admin receive the same notifications as any other employee for items addressed to them; pending moderation reports and marketplace listing approvals are reviewed through the Moderation Queue and Dashboard rather than as push notifications.</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="7" t="n">
+      <c r="D1" s="4"/>
+    </row>
+    <row r="2" spans="1:4" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Social Hub &amp; Feed Management</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>A company-wide social feed where employees can post text updates, photos, videos, polls, and announcements, and can edit or delete their own posts and comments. Each post's visibility can be set to everyone, a department, or a branch. People can react (Like, Love, Celebrate, Support, Insightful), comment, and tag colleagues. Polls are single-choice (a multi-choice option exists in the data model but has no UI control yet). HR and Admin can moderate content by hiding or removing posts, locking comments, and reviewing reported items.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="52.8" customHeight="1">
-      <c r="A5" s="9" t="n">
+      <c r="C2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>Recognition</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Lets employees recognize each other for things like teamwork, leadership, innovation, customer focus, excellence, and integrity, searching for the right colleague by name, Department, or Branch. Managers can also give recognition, and HR and Admin can award company-wide titles like Employee of the Month or Innovation Champion. Recognitions appear on a dedicated public wall, separate from the general Social Hub feed, where others can view and react to them.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="7" t="n">
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Surveys &amp; Feedback</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>A tool to build and send surveys using formats like short answer, long answer, multiple choice, checkboxes, dropdowns, rating scales, NPS, and matrix questions. Covers different survey types - engagement, satisfaction, pulse, event feedback, training feedback, or custom - and can be anonymous or named, mandatory or optional. Surveys can target the whole company, a department, or a branch, and are sent out immediately on publish. Results show participation rate along with average rating and NPS per question.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="79.2" customHeight="1">
-      <c r="A7" s="7" t="n">
+      <c r="C3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Marketplace</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>An internal marketplace where employees can negotiate, sell, request to buy, rent, exchange, or give away items in categories like electronics, furniture, books, vehicles, phones, appliances, and fashion. Each listing includes a title, description, category, price, photos, condition, and location, and can be searched or filtered the same way. Interested buyers can message the seller and track the conversation. Listings move through stages like draft, pending, active, or rejected; employee-submitted listings need HR or Admin approval before going live, while listings created by Admin go live immediately. Employees can also report listings that look fraudulent, inappropriate, or spammy.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="145.2" customHeight="1">
-      <c r="A8" s="12" t="n">
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Target-Based To-Do (Team &amp; Individual Tasks)</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Lets a supervisor create teams (naming members and, for HR/Admin, any supervisor) and assign to-do tasks or targets directly to one or more subordinates, with a clear description, due date, and priority, and cancel a task after it's assigned. Each task can be tracked through stages like assigned, in progress, and completed, with the subordinate able to update status and add progress notes, and reminders are sent as the due date approaches. Supervisors get a view of all tasks they've assigned, who's on track, and what's overdue, so follow-ups are easy without leaving the platform. A dedicated My Teams screen lists every team company-wide; a supervisor can edit or delete only the teams they personally supervise, while employees see only the team(s) they belong to in a read-only view. Supervisors, HR, and Admin can also assign a task directly to any employee company-wide, outside of a team, searchable by Department and Branch - these appear to the recipient as a separate Individual Tasks list with the same status tracking and reminders. Any employee can be assigned as supervisor of one team while being a subordinate or member of another, and can belong to more than one team at a time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="66" customHeight="1">
-      <c r="A9" s="12" t="n">
+      <c r="C4" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Dashboard Widgets</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>Quick-glance dashboards for three audiences. Employees see their pending surveys, recognition received, my tasks, and recent activity. Supervisors additionally see a team task overview - who's on track and what's overdue - for everyone assigned to them. HR and Admin see the same company-wide stats view - active surveys, average survey participation, total recognitions given, and pending marketplace listings awaiting approval; HR currently sees this admin-style view only, not a blended employee view (flagged in Known Gaps below).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="105.6" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Voting &amp; Election Management</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>A module enabling HR to organize secure and configurable elections where employees vote for nominated candidates — individual employees or teams, depending on the voting type. Elections can target the whole organization, a specific branch, department, team, or a hand-picked list of employees. HR configures single-choice or multiple-choice voting with minimum and maximum selectable candidates, and sets each election as anonymous (aggregated results only) or identified (HR can see each voter's identity and selections). HR can participate in voting when included in the eligible voter group.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Roles: Employee (any staff member) | Supervisor (an employee who supervises one or more teams, not a separate account type) | HR (an employee whose dashboard blends their own employee view with company-wide admin metrics) | Admin (a system administrator account, not an employee, with full company-wide access).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Status: Of Phase 1's 9 features, items 1–8 are fully implemented as a working prototype; item 9 (Voting &amp; Election Management) has been added to the Phase 1 scope and is not yet built. Phase 2 (Analytics, Global Search, Messenger) and Phase 4 (Events, Gamification) are not yet built; Phase 3 (AI Features) remains undecided.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Known Gaps &amp; Decisions Needed (from a code audit, before user stories are written): HR's dashboard is currently identical to Admin's rather than blending an employee view with company-wide stats - confirm intended behavior. Survey audience targeting for Department or Branch scope does not yet let you pick which department or branch, so it currently resolves to zero recipients - needs a fix before those scopes are usable. Team management and per-team task assignment pages have no route-level permission enforcement yet - access relies only on links being hidden in the UI, not real access control. Several modeled but unbuilt capabilities have no UI yet: survey matrix questions, marketplace listing edit/photos/My Listings, and editing or un-sending a recognition.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>Phase: 02 Analytic Features</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="66" customHeight="1"/>
-    <row r="17" ht="52.8" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>Analytics &amp; Reporting Dashboard</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>Provides comprehensive reporting and analytics across the platform to help management understand employee engagement, participation, and activity trends. Dashboards can display metrics such as active users, posts created, reactions, comments, survey participation rates, recognition activity, task completion rates, and marketplace usage. Reports can be filtered by date range, branch, department, division, designation, or grade, allowing HR and leadership to identify trends, measure engagement initiatives, and make data-driven decisions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="92.40000000000001" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>Global Search</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>A centralized search capability that allows employees to quickly find information across the entire platform. Users can search for employees, posts, comments, surveys, recognitions, marketplace listings, tasks, events, and other content using keywords or filters. Search results can be refined by category, department, date range, content type, or relevance, helping users locate information efficiently without navigating through multiple modules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>Messenger</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>A real-time private messaging tool that lets employees chat one-on-one or in groups directly within the platform. Users can send text messages, images, files, and voice notes, and see delivery/read receipts and typing indicators. Group chats support adding/removing members, naming the group, and assigning an admin. Employees can search past conversations, pin important chats, mute notifications for specific threads, and react to individual messages (like, love, etc.). Users can also share posts, marketplace listings, or event invites directly into a chat. HR and Admin can access moderation tools to review reported conversations for policy violations, without infringing on regular employee privacy. Notifications for new messages integrate with the platform's existing Notification Center.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22" ht="18" customHeight="1"/>
-    <row r="23">
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>Phase:3 AI Features</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Not decided yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29" ht="18" customHeight="1"/>
-    <row r="30" ht="52.8" customHeight="1">
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>Phase:4 Gamification Features</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="39.6" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>Events &amp; Activities Management</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>A platform for organizing and managing company events such as workshops, training programs, town halls, volunteer initiatives, sports activities, celebrations, and social gatherings. Events can include schedules, locations, participation limits, organizers, attachments, and announcements. Employees can browse upcoming events, view details, and stay informed about organizational activities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="52.8" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>Event Registration &amp; Attendance</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>Allows employees to register for events and indicate attendance status through options such as Going, Maybe, or Not Going. Organizers can monitor registrations, manage attendee lists, track participation, and send reminders before the event. Attendance records can be maintained for future reporting and engagement analysis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="52.8" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>Gamification &amp; Employee Engagement</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>A participation-based engagement system that encourages employees to actively contribute to the platform. Employees earn points for activities such as creating posts, receiving reactions, participating in surveys, attending events, completing assigned tasks, and recognizing colleagues. The system promotes healthy competition and motivates ongoing participation throughout the organization.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>Achievement Badges &amp; Recognition Levels</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>Allows employees to unlock achievement badges and progress through engagement levels based on milestones and participation. Examples include First Contributor, Team Player, Community Champion, Survey Advocate, and Recognition Star. Badges and levels are displayed on employee profiles and recognition feeds to celebrate accomplishments and encourage continued involvement.</t>
-        </is>
+      <c r="C5" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="79.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="145.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="12">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
+        <v>8</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="105.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="B15" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="66" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:3" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B23" s="20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:3" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>